--- a/artfynd/A 8179-2024 artfynd.xlsx
+++ b/artfynd/A 8179-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128642146</v>
       </c>
       <c r="B2" t="n">
-        <v>58055</v>
+        <v>58059</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128642145</v>
+        <v>128642144</v>
       </c>
       <c r="B3" t="n">
-        <v>79083</v>
+        <v>75175</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -792,21 +792,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -816,10 +816,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>814290</v>
+        <v>814291</v>
       </c>
       <c r="R3" t="n">
-        <v>7448098</v>
+        <v>7448102</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -882,10 +882,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128642144</v>
+        <v>128642145</v>
       </c>
       <c r="B4" t="n">
-        <v>75171</v>
+        <v>79087</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -893,21 +893,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -917,10 +917,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>814291</v>
+        <v>814290</v>
       </c>
       <c r="R4" t="n">
-        <v>7448102</v>
+        <v>7448098</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -986,7 +986,7 @@
         <v>128642137</v>
       </c>
       <c r="B5" t="n">
-        <v>82942</v>
+        <v>82946</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1087,7 +1087,7 @@
         <v>128642142</v>
       </c>
       <c r="B6" t="n">
-        <v>97449</v>
+        <v>97454</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 8179-2024 artfynd.xlsx
+++ b/artfynd/A 8179-2024 artfynd.xlsx
@@ -1087,7 +1087,7 @@
         <v>128642142</v>
       </c>
       <c r="B6" t="n">
-        <v>97454</v>
+        <v>97460</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 8179-2024 artfynd.xlsx
+++ b/artfynd/A 8179-2024 artfynd.xlsx
@@ -784,7 +784,7 @@
         <v>128642144</v>
       </c>
       <c r="B3" t="n">
-        <v>75175</v>
+        <v>75177</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -885,7 +885,7 @@
         <v>128642145</v>
       </c>
       <c r="B4" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -986,7 +986,7 @@
         <v>128642137</v>
       </c>
       <c r="B5" t="n">
-        <v>82946</v>
+        <v>82948</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1087,7 +1087,7 @@
         <v>128642142</v>
       </c>
       <c r="B6" t="n">
-        <v>97460</v>
+        <v>97462</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 8179-2024 artfynd.xlsx
+++ b/artfynd/A 8179-2024 artfynd.xlsx
@@ -1087,7 +1087,7 @@
         <v>128642142</v>
       </c>
       <c r="B6" t="n">
-        <v>97462</v>
+        <v>97463</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 8179-2024 artfynd.xlsx
+++ b/artfynd/A 8179-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128642146</v>
       </c>
       <c r="B2" t="n">
-        <v>58059</v>
+        <v>58086</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>128642144</v>
       </c>
       <c r="B3" t="n">
-        <v>75177</v>
+        <v>75204</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -885,7 +885,7 @@
         <v>128642145</v>
       </c>
       <c r="B4" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -986,7 +986,7 @@
         <v>128642137</v>
       </c>
       <c r="B5" t="n">
-        <v>82948</v>
+        <v>82975</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1087,7 +1087,7 @@
         <v>128642142</v>
       </c>
       <c r="B6" t="n">
-        <v>97463</v>
+        <v>97490</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 8179-2024 artfynd.xlsx
+++ b/artfynd/A 8179-2024 artfynd.xlsx
@@ -784,7 +784,7 @@
         <v>128642144</v>
       </c>
       <c r="B3" t="n">
-        <v>75204</v>
+        <v>75205</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -885,7 +885,7 @@
         <v>128642145</v>
       </c>
       <c r="B4" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -986,7 +986,7 @@
         <v>128642137</v>
       </c>
       <c r="B5" t="n">
-        <v>82975</v>
+        <v>82979</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1087,7 +1087,7 @@
         <v>128642142</v>
       </c>
       <c r="B6" t="n">
-        <v>97490</v>
+        <v>97496</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 8179-2024 artfynd.xlsx
+++ b/artfynd/A 8179-2024 artfynd.xlsx
@@ -1087,7 +1087,7 @@
         <v>128642142</v>
       </c>
       <c r="B6" t="n">
-        <v>97496</v>
+        <v>97503</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 8179-2024 artfynd.xlsx
+++ b/artfynd/A 8179-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128642146</v>
       </c>
       <c r="B2" t="n">
-        <v>58086</v>
+        <v>58090</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>128642144</v>
       </c>
       <c r="B3" t="n">
-        <v>75205</v>
+        <v>75209</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -885,7 +885,7 @@
         <v>128642145</v>
       </c>
       <c r="B4" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -986,7 +986,7 @@
         <v>128642137</v>
       </c>
       <c r="B5" t="n">
-        <v>82979</v>
+        <v>82983</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1087,7 +1087,7 @@
         <v>128642142</v>
       </c>
       <c r="B6" t="n">
-        <v>97503</v>
+        <v>97507</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 8179-2024 artfynd.xlsx
+++ b/artfynd/A 8179-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128642146</v>
       </c>
       <c r="B2" t="n">
-        <v>58090</v>
+        <v>58093</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>128642144</v>
       </c>
       <c r="B3" t="n">
-        <v>75209</v>
+        <v>83005</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -885,7 +885,7 @@
         <v>128642145</v>
       </c>
       <c r="B4" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -986,7 +986,7 @@
         <v>128642137</v>
       </c>
       <c r="B5" t="n">
-        <v>82983</v>
+        <v>82892</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1087,7 +1087,7 @@
         <v>128642142</v>
       </c>
       <c r="B6" t="n">
-        <v>97507</v>
+        <v>97514</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 8179-2024 artfynd.xlsx
+++ b/artfynd/A 8179-2024 artfynd.xlsx
@@ -784,7 +784,7 @@
         <v>128642144</v>
       </c>
       <c r="B3" t="n">
-        <v>83005</v>
+        <v>83010</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -885,7 +885,7 @@
         <v>128642145</v>
       </c>
       <c r="B4" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -986,7 +986,7 @@
         <v>128642137</v>
       </c>
       <c r="B5" t="n">
-        <v>82892</v>
+        <v>82897</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1087,7 +1087,7 @@
         <v>128642142</v>
       </c>
       <c r="B6" t="n">
-        <v>97517</v>
+        <v>97522</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 8179-2024 artfynd.xlsx
+++ b/artfynd/A 8179-2024 artfynd.xlsx
@@ -784,7 +784,7 @@
         <v>128642144</v>
       </c>
       <c r="B3" t="n">
-        <v>83010</v>
+        <v>83011</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -885,7 +885,7 @@
         <v>128642145</v>
       </c>
       <c r="B4" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -986,7 +986,7 @@
         <v>128642137</v>
       </c>
       <c r="B5" t="n">
-        <v>82897</v>
+        <v>82898</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1087,7 +1087,7 @@
         <v>128642142</v>
       </c>
       <c r="B6" t="n">
-        <v>97522</v>
+        <v>97530</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 8179-2024 artfynd.xlsx
+++ b/artfynd/A 8179-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128642146</v>
       </c>
       <c r="B2" t="n">
-        <v>58093</v>
+        <v>58095</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>128642144</v>
       </c>
       <c r="B3" t="n">
-        <v>83011</v>
+        <v>83015</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -885,7 +885,7 @@
         <v>128642145</v>
       </c>
       <c r="B4" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -986,7 +986,7 @@
         <v>128642137</v>
       </c>
       <c r="B5" t="n">
-        <v>82898</v>
+        <v>82902</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1087,7 +1087,7 @@
         <v>128642142</v>
       </c>
       <c r="B6" t="n">
-        <v>97530</v>
+        <v>97540</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 8179-2024 artfynd.xlsx
+++ b/artfynd/A 8179-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,50 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128642146</v>
+        <v>128642131</v>
       </c>
       <c r="B2" t="n">
-        <v>58095</v>
+        <v>83173</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103015</v>
+        <v>1312</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Petäjävaara, Nb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>814382</v>
+        <v>814537</v>
       </c>
       <c r="R2" t="n">
-        <v>7448062</v>
+        <v>7447844</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128642144</v>
+        <v>128642137</v>
       </c>
       <c r="B3" t="n">
-        <v>83015</v>
+        <v>83173</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -792,21 +787,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6440</v>
+        <v>1312</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -816,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>814291</v>
+        <v>814473</v>
       </c>
       <c r="R3" t="n">
-        <v>7448102</v>
+        <v>7447980</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -882,14 +877,14 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128642145</v>
+        <v>128642136</v>
       </c>
       <c r="B4" t="n">
-        <v>79039</v>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -917,10 +912,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>814290</v>
+        <v>814541</v>
       </c>
       <c r="R4" t="n">
-        <v>7448098</v>
+        <v>7447990</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -983,32 +978,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128642137</v>
+        <v>128642145</v>
       </c>
       <c r="B5" t="n">
-        <v>82902</v>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1018,10 +1013,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>814473</v>
+        <v>814290</v>
       </c>
       <c r="R5" t="n">
-        <v>7447980</v>
+        <v>7448098</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1084,32 +1079,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128642142</v>
+        <v>128642150</v>
       </c>
       <c r="B6" t="n">
-        <v>97540</v>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1119,10 +1114,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>814307</v>
+        <v>814428</v>
       </c>
       <c r="R6" t="n">
-        <v>7448107</v>
+        <v>7448105</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1178,6 +1173,617 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>128642144</v>
+      </c>
+      <c r="B7" t="n">
+        <v>83307</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Petäjävaara, Nb</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>814291</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7448102</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Tärendö</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-08-13</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-08-13</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Noomi Berg</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Noomi Berg</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>128642135</v>
+      </c>
+      <c r="B8" t="n">
+        <v>80461</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Petäjävaara, Nb</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>814527</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7447966</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Tärendö</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-08-13</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-08-13</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Noomi Berg</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Noomi Berg</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>128642146</v>
+      </c>
+      <c r="B9" t="n">
+        <v>58327</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Petäjävaara, Nb</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>814382</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7448062</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Tärendö</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-08-13</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-08-13</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Noomi Berg</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Noomi Berg</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>128642149</v>
+      </c>
+      <c r="B10" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Petäjävaara, Nb</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>814452</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7448108</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Tärendö</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-08-13</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-08-13</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Noomi Berg</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Noomi Berg</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>128642142</v>
+      </c>
+      <c r="B11" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Petäjävaara, Nb</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>814307</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7448107</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Tärendö</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-08-13</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-08-13</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Noomi Berg</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Noomi Berg</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>128642127</v>
+      </c>
+      <c r="B12" t="n">
+        <v>92329</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6040186</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Kötticka</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Leptoporus mollis</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Pers.:Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Petäjävaara, Nb</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>814544</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7447845</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Tärendö</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-08-13</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-08-13</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Noomi Berg</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Noomi Berg</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
         <is>
           <t>Ecogain</t>
         </is>
